--- a/output/pdf_financials_xlsx/EVGN.xlsx
+++ b/output/pdf_financials_xlsx/EVGN.xlsx
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.543</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>6.933</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>6.066</v>
       </c>
     </row>
     <row r="71">
@@ -2242,19 +2242,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>6.458</v>
+        <v>6.756</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>5.759</v>
+        <v>6.302</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>14.682</v>
+        <v>15.491</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>17.682</v>
+        <v>24.615</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>16.091</v>
+        <v>22.157</v>
       </c>
     </row>
     <row r="72">
@@ -2440,19 +2440,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.1052271394121098</v>
+        <v>0.1100827739034087</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.09019859666708432</v>
+        <v>0.09870317002881844</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.2453706798582793</v>
+        <v>0.2588909686476369</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.3967420570813139</v>
+        <v>0.5523021001615509</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.3526485349229657</v>
+        <v>0.485590304411668</v>
       </c>
     </row>
     <row r="81">
@@ -3019,19 +3019,19 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>1.389</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.742</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="108">
@@ -3141,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="113">
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.466</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -4518,7 +4518,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.298</v>
       </c>
@@ -6519,7 +6523,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -10351,7 +10359,11 @@
           <t>Share-based payment expense 16c</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -10509,7 +10521,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -10870,7 +10886,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -11211,7 +11231,11 @@
           <t>Proceeds from private placement 16</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -11769,7 +11793,11 @@
           <t>Share-based payment expense 13c</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -11925,7 +11953,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -12821,7 +12853,11 @@
           <t>Share-based payment expense 15d</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -13625,7 +13661,11 @@
           <t>Repurchase of common shares 15e</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -13834,7 +13874,11 @@
           <t>Share-based payment expense 15e</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E255" s="5" t="n">
         <v>1.389</v>
       </c>
@@ -13953,7 +13997,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>-0.412</v>
       </c>
@@ -14560,7 +14608,11 @@
           <t>Repurchase of common shares 15f</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
